--- a/salidas/empresas/PFE.xlsx
+++ b/salidas/empresas/PFE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>9.894305229187012</v>
+        <v>9.894304275512695</v>
       </c>
       <c r="C2" t="n">
         <v>24.36432647705078</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>10.18791103363037</v>
+        <v>10.18790912628174</v>
       </c>
       <c r="C3" t="n">
         <v>24.84819793701172</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>9.693878173828125</v>
+        <v>9.693875312805176</v>
       </c>
       <c r="C4" t="n">
         <v>23.64326477050781</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>9.85336971282959</v>
+        <v>9.853368759155273</v>
       </c>
       <c r="C5" t="n">
         <v>24.03225708007812</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>9.29115104675293</v>
+        <v>9.291153907775879</v>
       </c>
       <c r="C6" t="n">
         <v>22.44781875610352</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>9.216537475585938</v>
+        <v>9.216541290283203</v>
       </c>
       <c r="C7" t="n">
         <v>22.26755142211914</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>10.20613098144531</v>
+        <v>10.20612812042236</v>
       </c>
       <c r="C8" t="n">
         <v>24.65844345092773</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>10.9228687286377</v>
+        <v>10.92287254333496</v>
       </c>
       <c r="C9" t="n">
         <v>26.14800834655762</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.23993396759033</v>
+        <v>11.23993110656738</v>
       </c>
       <c r="C10" t="n">
         <v>26.90702056884766</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>10.56220722198486</v>
+        <v>10.56220436096191</v>
       </c>
       <c r="C11" t="n">
         <v>25.28462982177734</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>10.35604000091553</v>
+        <v>10.35603809356689</v>
       </c>
       <c r="C13" t="n">
         <v>24.57305526733398</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>10.49198055267334</v>
+        <v>10.49198627471924</v>
       </c>
       <c r="C14" t="n">
         <v>24.8956356048584</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>10.08923053741455</v>
+        <v>10.08923244476318</v>
       </c>
       <c r="C15" t="n">
         <v>23.68121337890625</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.69555759429932</v>
+        <v>10.69555473327637</v>
       </c>
       <c r="C17" t="n">
         <v>25.1043643951416</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>11.23098564147949</v>
+        <v>11.23098468780518</v>
       </c>
       <c r="C18" t="n">
         <v>26.08159446716309</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>10.44657230377197</v>
+        <v>10.44657325744629</v>
       </c>
       <c r="C19" t="n">
         <v>24.25996208190918</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>9.604965209960938</v>
+        <v>9.604966163635254</v>
       </c>
       <c r="C20" t="n">
         <v>22.30550384521484</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>10.10112762451172</v>
+        <v>10.1011266708374</v>
       </c>
       <c r="C22" t="n">
         <v>23.17836761474609</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>10.17555046081543</v>
+        <v>10.17555141448975</v>
       </c>
       <c r="C23" t="n">
         <v>23.34914588928223</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>9.944615364074707</v>
+        <v>9.94461727142334</v>
       </c>
       <c r="C24" t="n">
         <v>22.54269409179688</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>9.513517379760742</v>
+        <v>9.513511657714844</v>
       </c>
       <c r="C25" t="n">
         <v>21.56546592712402</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>9.456972122192383</v>
+        <v>9.456976890563965</v>
       </c>
       <c r="C27" t="n">
         <v>21.13851928710938</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>8.535897254943848</v>
+        <v>8.535895347595215</v>
       </c>
       <c r="C29" t="n">
         <v>19.07969665527344</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>8.348377227783203</v>
+        <v>8.34837818145752</v>
       </c>
       <c r="C30" t="n">
         <v>18.36812019348145</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>7.533377170562744</v>
+        <v>7.53337574005127</v>
       </c>
       <c r="C31" t="n">
         <v>16.57495307922363</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>8.376571655273438</v>
+        <v>8.376568794250488</v>
       </c>
       <c r="C33" t="n">
         <v>18.13092994689941</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>8.082884788513184</v>
+        <v>8.0828857421875</v>
       </c>
       <c r="C34" t="n">
         <v>17.4952564239502</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>7.762905120849609</v>
+        <v>7.762901306152344</v>
       </c>
       <c r="C35" t="n">
         <v>16.80265617370605</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>7.329228401184082</v>
+        <v>7.329229831695557</v>
       </c>
       <c r="C36" t="n">
         <v>15.58823490142822</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>7.900226593017578</v>
+        <v>7.900221347808838</v>
       </c>
       <c r="C37" t="n">
         <v>16.80265617370605</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.503967761993408</v>
+        <v>6.503966808319092</v>
       </c>
       <c r="C38" t="n">
         <v>13.83301734924316</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.609440326690674</v>
+        <v>5.609440803527832</v>
       </c>
       <c r="C39" t="n">
         <v>11.67931747436523</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>6.206382751464844</v>
+        <v>6.20638370513916</v>
       </c>
       <c r="C40" t="n">
         <v>12.92220115661621</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>6.087905883789062</v>
+        <v>6.087904453277588</v>
       </c>
       <c r="C41" t="n">
         <v>12.67552185058594</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>7.000236988067627</v>
+        <v>7.000235080718994</v>
       </c>
       <c r="C42" t="n">
         <v>14.41176509857178</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>6.912678241729736</v>
+        <v>6.912675380706787</v>
       </c>
       <c r="C43" t="n">
         <v>14.23149871826172</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>7.341262817382812</v>
+        <v>7.341259002685547</v>
       </c>
       <c r="C44" t="n">
         <v>15.11385154724121</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>7.773510932922363</v>
+        <v>7.773512840270996</v>
       </c>
       <c r="C45" t="n">
         <v>15.84440231323242</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>7.70368766784668</v>
+        <v>7.703690528869629</v>
       </c>
       <c r="C46" t="n">
         <v>15.70208740234375</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>7.927120685577393</v>
+        <v>7.927116870880127</v>
       </c>
       <c r="C47" t="n">
         <v>16.15749549865723</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>8.538649559020996</v>
+        <v>8.538652420043945</v>
       </c>
       <c r="C48" t="n">
         <v>17.23908805847168</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.548048973083496</v>
+        <v>8.548052787780762</v>
       </c>
       <c r="C49" t="n">
         <v>17.25806427001953</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>8.768918991088867</v>
+        <v>8.768918037414551</v>
       </c>
       <c r="C50" t="n">
         <v>17.7039852142334</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.325180053710938</v>
+        <v>8.325183868408203</v>
       </c>
       <c r="C51" t="n">
         <v>16.65085411071777</v>
@@ -1474,7 +1486,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>7.931454181671143</v>
+        <v>7.931455135345459</v>
       </c>
       <c r="C53" t="n">
         <v>15.86337757110596</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.300782203674316</v>
+        <v>7.300779342651367</v>
       </c>
       <c r="C54" t="n">
         <v>14.44971466064453</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>6.835795402526855</v>
+        <v>6.835793972015381</v>
       </c>
       <c r="C55" t="n">
         <v>13.52941226959229</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>7.190526962280273</v>
+        <v>7.190529823303223</v>
       </c>
       <c r="C56" t="n">
         <v>14.23149871826172</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>7.711705207824707</v>
+        <v>7.711703300476074</v>
       </c>
       <c r="C57" t="n">
         <v>15.09487724304199</v>
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>8.443611145019531</v>
+        <v>8.443610191345215</v>
       </c>
       <c r="C59" t="n">
         <v>16.52751350402832</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>7.982422828674316</v>
+        <v>7.982423782348633</v>
       </c>
       <c r="C60" t="n">
         <v>15.4648962020874</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>8.574984550476074</v>
+        <v>8.574986457824707</v>
       </c>
       <c r="C61" t="n">
         <v>16.6129035949707</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>8.922686576843262</v>
+        <v>8.922687530517578</v>
       </c>
       <c r="C62" t="n">
         <v>17.28652763366699</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>9.521276473999023</v>
+        <v>9.521273612976074</v>
       </c>
       <c r="C63" t="n">
         <v>18.25426864624023</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>10.05078506469727</v>
+        <v>10.0507869720459</v>
       </c>
       <c r="C64" t="n">
         <v>19.26944923400879</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>10.37740135192871</v>
+        <v>10.37739658355713</v>
       </c>
       <c r="C65" t="n">
         <v>19.8956356048584</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.71769142150879</v>
+        <v>10.71769332885742</v>
       </c>
       <c r="C66" t="n">
         <v>20.35104370117188</v>
@@ -1865,7 +1877,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1894,7 +1906,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>9.589262962341309</v>
+        <v>9.58925724029541</v>
       </c>
       <c r="C69" t="n">
         <v>18.00758934020996</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>8.932465553283691</v>
+        <v>8.932462692260742</v>
       </c>
       <c r="C70" t="n">
         <v>16.77419471740723</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>9.730722427368164</v>
+        <v>9.730728149414062</v>
       </c>
       <c r="C71" t="n">
         <v>18.27324485778809</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>10.24202728271484</v>
+        <v>10.24202632904053</v>
       </c>
       <c r="C72" t="n">
         <v>19.04174613952637</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.04322052001953</v>
+        <v>11.04321670532227</v>
       </c>
       <c r="C73" t="n">
         <v>20.53130912780762</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>10.92074203491211</v>
+        <v>10.92073917388916</v>
       </c>
       <c r="C74" t="n">
         <v>20.30360412597656</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>10.8949613571167</v>
+        <v>10.89496326446533</v>
       </c>
       <c r="C75" t="n">
         <v>20.04743766784668</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>11.67870044708252</v>
+        <v>11.6786994934082</v>
       </c>
       <c r="C76" t="n">
         <v>21.48956489562988</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>11.80760097503662</v>
+        <v>11.80759906768799</v>
       </c>
       <c r="C77" t="n">
         <v>21.72675514221191</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>11.38826370239258</v>
+        <v>11.38826942443848</v>
       </c>
       <c r="C78" t="n">
         <v>20.74952507019043</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>11.9766845703125</v>
+        <v>11.97668743133545</v>
       </c>
       <c r="C79" t="n">
         <v>21.82163238525391</v>
@@ -2242,7 +2254,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>12.53926372528076</v>
+        <v>12.53926467895508</v>
       </c>
       <c r="C81" t="n">
         <v>22.63757133483887</v>
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>13.07005310058594</v>
+        <v>13.0700569152832</v>
       </c>
       <c r="C83" t="n">
         <v>23.5958251953125</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>13.26700496673584</v>
+        <v>13.26700401306152</v>
       </c>
       <c r="C84" t="n">
         <v>23.73814010620117</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>13.29881858825684</v>
+        <v>13.29882144927979</v>
       </c>
       <c r="C85" t="n">
         <v>23.79506683349609</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>14.5918140411377</v>
+        <v>14.59181499481201</v>
       </c>
       <c r="C86" t="n">
         <v>25.88235282897949</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>14.63994693756104</v>
+        <v>14.63995265960693</v>
       </c>
       <c r="C87" t="n">
         <v>25.96774291992188</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>15.43693447113037</v>
+        <v>15.43693542480469</v>
       </c>
       <c r="C88" t="n">
         <v>27.38140487670898</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>15.54926300048828</v>
+        <v>15.5492639541626</v>
       </c>
       <c r="C89" t="n">
         <v>27.58064460754395</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>14.68648338317871</v>
+        <v>14.68648719787598</v>
       </c>
       <c r="C90" t="n">
         <v>25.83491516113281</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>15.10717487335205</v>
+        <v>15.10717582702637</v>
       </c>
       <c r="C91" t="n">
         <v>26.57495307922363</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>15.89374542236328</v>
+        <v>15.89374446868896</v>
       </c>
       <c r="C92" t="n">
         <v>27.73244857788086</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>15.33911800384521</v>
+        <v>15.33912467956543</v>
       </c>
       <c r="C93" t="n">
         <v>26.76470565795898</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>15.62186717987061</v>
+        <v>15.62187385559082</v>
       </c>
       <c r="C94" t="n">
         <v>27.25806427001953</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>16.68761825561523</v>
+        <v>16.68761253356934</v>
       </c>
       <c r="C95" t="n">
         <v>29.11764717102051</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>17.38669204711914</v>
+        <v>17.38669013977051</v>
       </c>
       <c r="C96" t="n">
         <v>30.1043643951416</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>16.78393936157227</v>
+        <v>16.78393363952637</v>
       </c>
       <c r="C97" t="n">
         <v>29.06072044372559</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65790557861328</v>
+        <v>16.65790748596191</v>
       </c>
       <c r="C98" t="n">
         <v>28.84250450134277</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>17.74163627624512</v>
+        <v>17.74163055419922</v>
       </c>
       <c r="C99" t="n">
         <v>30.46489524841309</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.74715232849121</v>
+        <v>17.74715423583984</v>
       </c>
       <c r="C100" t="n">
         <v>30.4743824005127</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>17.28302955627441</v>
+        <v>17.28303146362305</v>
       </c>
       <c r="C101" t="n">
         <v>29.67741966247559</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>16.51728630065918</v>
+        <v>16.51728820800781</v>
       </c>
       <c r="C102" t="n">
         <v>28.11195373535156</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>16.5451602935791</v>
+        <v>16.54515647888184</v>
       </c>
       <c r="C103" t="n">
         <v>28.15939331054688</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>16.1400089263916</v>
+        <v>16.14000511169434</v>
       </c>
       <c r="C104" t="n">
         <v>27.2296028137207</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>16.52803993225098</v>
+        <v>16.52803611755371</v>
       </c>
       <c r="C105" t="n">
         <v>27.88425064086914</v>
@@ -2996,7 +3008,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>16.84296798706055</v>
+        <v>16.84296607971191</v>
       </c>
       <c r="C107" t="n">
         <v>28.41555976867676</v>
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>17.72625160217285</v>
+        <v>17.72625541687012</v>
       </c>
       <c r="C110" t="n">
         <v>29.64895629882812</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>19.63941955566406</v>
+        <v>19.63942337036133</v>
       </c>
       <c r="C111" t="n">
         <v>32.56166839599609</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.90837669372559</v>
+        <v>19.90837478637695</v>
       </c>
       <c r="C112" t="n">
         <v>33.00759124755859</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>19.4162425994873</v>
+        <v>19.41625022888184</v>
       </c>
       <c r="C113" t="n">
         <v>32.191650390625</v>
@@ -3228,7 +3240,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3286,7 +3298,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>18.73554229736328</v>
+        <v>18.73554039001465</v>
       </c>
       <c r="C117" t="n">
         <v>30.56925964355469</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>18.26453399658203</v>
+        <v>18.26453971862793</v>
       </c>
       <c r="C118" t="n">
         <v>29.80075836181641</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>19.66592979431152</v>
+        <v>19.66592597961426</v>
       </c>
       <c r="C119" t="n">
         <v>32.08728790283203</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>19.20917320251465</v>
+        <v>19.20916175842285</v>
       </c>
       <c r="C120" t="n">
         <v>31.0910816192627</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>18.92193412780762</v>
+        <v>18.92193603515625</v>
       </c>
       <c r="C121" t="n">
         <v>30.62618637084961</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>17.87267112731934</v>
+        <v>17.87267303466797</v>
       </c>
       <c r="C122" t="n">
         <v>28.92789459228516</v>
@@ -3489,7 +3501,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3518,7 +3530,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>19.36676406860352</v>
+        <v>19.36676025390625</v>
       </c>
       <c r="C125" t="n">
         <v>31.03415679931641</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>20.72898101806641</v>
+        <v>20.72897529602051</v>
       </c>
       <c r="C126" t="n">
         <v>32.92219924926758</v>
@@ -3605,7 +3617,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3634,7 +3646,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>20.96151924133301</v>
+        <v>20.96152305603027</v>
       </c>
       <c r="C129" t="n">
         <v>33.0170783996582</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>20.40134429931641</v>
+        <v>20.40134620666504</v>
       </c>
       <c r="C130" t="n">
         <v>32.13472366333008</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>19.10028076171875</v>
+        <v>19.10028648376465</v>
       </c>
       <c r="C131" t="n">
         <v>30.08538818359375</v>
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>19.75921249389648</v>
+        <v>19.75921058654785</v>
       </c>
       <c r="C133" t="n">
         <v>30.81593894958496</v>
@@ -3808,7 +3820,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>20.9683666229248</v>
+        <v>20.96836471557617</v>
       </c>
       <c r="C135" t="n">
         <v>32.37191772460938</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>21.02367973327637</v>
+        <v>21.023681640625</v>
       </c>
       <c r="C136" t="n">
         <v>32.45730590820312</v>
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>20.84546089172363</v>
+        <v>20.84546279907227</v>
       </c>
       <c r="C137" t="n">
         <v>32.18216323852539</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>20.25919914245605</v>
+        <v>20.25920104980469</v>
       </c>
       <c r="C138" t="n">
         <v>30.97723007202148</v>
@@ -3953,7 +3965,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>20.57565689086914</v>
+        <v>20.57566452026367</v>
       </c>
       <c r="C140" t="n">
         <v>31.46110153198242</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>21.2528190612793</v>
+        <v>21.25282096862793</v>
       </c>
       <c r="C141" t="n">
         <v>32.18216323852539</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>22.36809730529785</v>
+        <v>22.36809539794922</v>
       </c>
       <c r="C142" t="n">
         <v>33.87096786499023</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>21.96709251403809</v>
+        <v>21.96709823608398</v>
       </c>
       <c r="C143" t="n">
         <v>33.26375579833984</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>22.92655944824219</v>
+        <v>22.92656707763672</v>
       </c>
       <c r="C144" t="n">
         <v>34.40227890014648</v>
@@ -4127,7 +4139,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>23.41974830627441</v>
+        <v>23.41974449157715</v>
       </c>
       <c r="C146" t="n">
         <v>35.14231491088867</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>23.17087173461914</v>
+        <v>23.17086791992188</v>
       </c>
       <c r="C147" t="n">
         <v>34.44971466064453</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>22.64759635925293</v>
+        <v>22.64759254455566</v>
       </c>
       <c r="C148" t="n">
         <v>33.67172622680664</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>23.36231994628906</v>
+        <v>23.36231231689453</v>
       </c>
       <c r="C149" t="n">
         <v>34.73434448242188</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>23.15219688415527</v>
+        <v>23.15220069885254</v>
       </c>
       <c r="C150" t="n">
         <v>34.08918380737305</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>23.37773323059082</v>
+        <v>23.37773132324219</v>
       </c>
       <c r="C151" t="n">
         <v>34.4212532043457</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>25.72966957092285</v>
+        <v>25.72967529296875</v>
       </c>
       <c r="C152" t="n">
         <v>37.88425064086914</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>26.98203659057617</v>
+        <v>26.98202896118164</v>
       </c>
       <c r="C153" t="n">
         <v>39.39278793334961</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>28.6391773223877</v>
+        <v>28.63916015625</v>
       </c>
       <c r="C154" t="n">
         <v>41.8121452331543</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>27.98280906677246</v>
+        <v>27.9828052520752</v>
       </c>
       <c r="C155" t="n">
         <v>40.85388946533203</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>30.27467918395996</v>
+        <v>30.27468681335449</v>
       </c>
       <c r="C156" t="n">
         <v>43.86148071289062</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>28.58511924743652</v>
+        <v>28.58511734008789</v>
       </c>
       <c r="C157" t="n">
         <v>41.41366195678711</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>28.04206085205078</v>
+        <v>28.04206848144531</v>
       </c>
       <c r="C158" t="n">
         <v>40.27514266967773</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>28.63659858703613</v>
+        <v>28.6365966796875</v>
       </c>
       <c r="C159" t="n">
         <v>41.12903213500977</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>28.05527496337891</v>
+        <v>28.05527114868164</v>
       </c>
       <c r="C160" t="n">
         <v>40.29411697387695</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>26.82657051086426</v>
+        <v>26.82657432556152</v>
       </c>
       <c r="C161" t="n">
         <v>38.52941131591797</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>27.67097473144531</v>
+        <v>27.67097091674805</v>
       </c>
       <c r="C162" t="n">
         <v>39.39278793334961</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>28.87058639526367</v>
+        <v>28.87057876586914</v>
       </c>
       <c r="C163" t="n">
         <v>41.10057067871094</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>25.8848876953125</v>
+        <v>25.88489151000977</v>
       </c>
       <c r="C164" t="n">
         <v>36.85009384155273</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>23.91392707824707</v>
+        <v>23.91392135620117</v>
       </c>
       <c r="C165" t="n">
         <v>33.72865295410156</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>24.1695499420166</v>
+        <v>24.16954803466797</v>
       </c>
       <c r="C166" t="n">
         <v>34.08918380737305</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>25.81089401245117</v>
+        <v>25.8108959197998</v>
       </c>
       <c r="C167" t="n">
         <v>36.4041748046875</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>26.1622200012207</v>
+        <v>26.1622257232666</v>
       </c>
       <c r="C168" t="n">
         <v>36.54648971557617</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>26.61048316955566</v>
+        <v>26.61048698425293</v>
       </c>
       <c r="C169" t="n">
         <v>37.17267608642578</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>25.55122947692871</v>
+        <v>25.55123138427734</v>
       </c>
       <c r="C170" t="n">
         <v>35.33206939697266</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>22.93024444580078</v>
+        <v>22.93024063110352</v>
       </c>
       <c r="C171" t="n">
         <v>31.7077808380127</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>22.39506721496582</v>
+        <v>22.39506912231445</v>
       </c>
       <c r="C172" t="n">
         <v>30.96774291992188</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>26.31968307495117</v>
+        <v>26.3196907043457</v>
       </c>
       <c r="C173" t="n">
         <v>36.39468765258789</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>26.46418952941895</v>
+        <v>26.46418571472168</v>
       </c>
       <c r="C174" t="n">
         <v>36.2333984375</v>
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>26.92575263977051</v>
+        <v>26.92575645446777</v>
       </c>
       <c r="C176" t="n">
         <v>36.50853729248047</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>26.44294357299805</v>
+        <v>26.44294738769531</v>
       </c>
       <c r="C177" t="n">
         <v>35.85388946533203</v>
@@ -5084,11 +5096,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>25.68023681640625</v>
+        <v>25.68023300170898</v>
       </c>
       <c r="C178" t="n">
         <v>34.81973266601562</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>24.82655906677246</v>
+        <v>24.82655715942383</v>
       </c>
       <c r="C179" t="n">
         <v>33.66223907470703</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>28.54495429992676</v>
+        <v>28.54494285583496</v>
       </c>
       <c r="C180" t="n">
         <v>38.31000137329102</v>
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>27.42729759216309</v>
+        <v>27.42728996276855</v>
       </c>
       <c r="C181" t="n">
         <v>36.81000137329102</v>
@@ -5200,11 +5212,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>27.04023933410645</v>
+        <v>27.04024505615234</v>
       </c>
       <c r="C182" t="n">
         <v>35.90000152587891</v>
@@ -5229,11 +5241,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>25.22500419616699</v>
+        <v>25.22501182556152</v>
       </c>
       <c r="C183" t="n">
         <v>33.4900016784668</v>
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>27.28880500793457</v>
+        <v>27.28879737854004</v>
       </c>
       <c r="C184" t="n">
         <v>36.22999954223633</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>29.11157608032227</v>
+        <v>29.1115608215332</v>
       </c>
       <c r="C185" t="n">
         <v>38.65000152587891</v>
@@ -5316,11 +5328,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>29.45927047729492</v>
+        <v>29.45927238464355</v>
       </c>
       <c r="C186" t="n">
         <v>38.72999954223633</v>
@@ -5345,7 +5357,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>32.85757446289062</v>
+        <v>32.85758209228516</v>
       </c>
       <c r="C188" t="n">
         <v>42.81000137329102</v>
@@ -5403,11 +5415,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>35.35968780517578</v>
+        <v>35.35969161987305</v>
       </c>
       <c r="C189" t="n">
         <v>46.06999969482422</v>
@@ -5432,7 +5444,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5461,11 +5473,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>33.57137680053711</v>
+        <v>33.57136917114258</v>
       </c>
       <c r="C191" t="n">
         <v>43.7400016784668</v>
@@ -5490,7 +5502,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5519,11 +5531,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>45.71994018554688</v>
+        <v>45.71992874145508</v>
       </c>
       <c r="C193" t="n">
         <v>59.04999923706055</v>
@@ -5548,7 +5560,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5577,11 +5589,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>36.62000274658203</v>
+        <v>36.61999893188477</v>
       </c>
       <c r="C195" t="n">
         <v>46.93999862670898</v>
@@ -5606,11 +5618,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>40.38811111450195</v>
+        <v>40.38810348510742</v>
       </c>
       <c r="C196" t="n">
         <v>51.77000045776367</v>
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>38.28171157836914</v>
+        <v>38.28170776367188</v>
       </c>
       <c r="C197" t="n">
         <v>49.06999969482422</v>
@@ -5664,7 +5676,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5693,11 +5705,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>41.2365608215332</v>
+        <v>41.23655700683594</v>
       </c>
       <c r="C199" t="n">
         <v>52.43000030517578</v>
@@ -5722,11 +5734,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>40.03472518920898</v>
+        <v>40.03472900390625</v>
       </c>
       <c r="C200" t="n">
         <v>50.5099983215332</v>
@@ -5751,7 +5763,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5780,11 +5792,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>34.68460845947266</v>
+        <v>34.68460464477539</v>
       </c>
       <c r="C202" t="n">
         <v>43.7599983215332</v>
@@ -5809,11 +5821,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>36.8959846496582</v>
+        <v>36.89599609375</v>
       </c>
       <c r="C203" t="n">
         <v>46.54999923706055</v>
@@ -5838,11 +5850,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>40.07408142089844</v>
+        <v>40.07407379150391</v>
       </c>
       <c r="C204" t="n">
         <v>50.13000106811523</v>
@@ -5867,7 +5879,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5896,11 +5908,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>35.625732421875</v>
+        <v>35.62572860717773</v>
       </c>
       <c r="C206" t="n">
         <v>44.15999984741211</v>
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>32.72953033447266</v>
+        <v>32.72952651977539</v>
       </c>
       <c r="C207" t="n">
         <v>40.56999969482422</v>
@@ -5954,11 +5966,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>32.91507720947266</v>
+        <v>32.91508102416992</v>
       </c>
       <c r="C208" t="n">
         <v>40.79999923706055</v>
@@ -5983,11 +5995,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>31.37419891357422</v>
+        <v>31.37420082092285</v>
       </c>
       <c r="C209" t="n">
         <v>38.88999938964844</v>
@@ -6012,11 +6024,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>31.00423049926758</v>
+        <v>31.00423240661621</v>
       </c>
       <c r="C210" t="n">
         <v>38.02000045776367</v>
@@ -6041,11 +6053,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>29.91150283813477</v>
+        <v>29.91149711608887</v>
       </c>
       <c r="C211" t="n">
         <v>36.68000030517578</v>
@@ -6070,11 +6082,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>29.7335319519043</v>
+        <v>29.73352813720703</v>
       </c>
       <c r="C212" t="n">
         <v>36.06000137329102</v>
@@ -6099,11 +6111,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>29.17283058166504</v>
+        <v>29.17282867431641</v>
       </c>
       <c r="C213" t="n">
         <v>35.38000106811523</v>
@@ -6128,7 +6140,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6157,7 +6169,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6186,7 +6198,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6215,7 +6227,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6244,7 +6256,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6273,11 +6285,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>22.52950668334961</v>
+        <v>22.52950859069824</v>
       </c>
       <c r="C219" t="n">
         <v>26.55999946594238</v>
@@ -6302,11 +6314,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>23.53892517089844</v>
+        <v>23.5389232635498</v>
       </c>
       <c r="C220" t="n">
         <v>27.75</v>
@@ -6331,11 +6343,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>21.73215484619141</v>
+        <v>21.73215293884277</v>
       </c>
       <c r="C221" t="n">
         <v>25.6200008392334</v>
@@ -6360,7 +6372,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6387,7 +6399,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6414,11 +6426,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>26.66733360290527</v>
+        <v>26.66733741760254</v>
       </c>
       <c r="C224" t="n">
         <v>30.54000091552734</v>
@@ -6441,11 +6453,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>25.33135032653809</v>
+        <v>25.33134841918945</v>
       </c>
       <c r="C225" t="n">
         <v>29.01000022888184</v>
@@ -6468,11 +6480,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>25.27022552490234</v>
+        <v>25.27022361755371</v>
       </c>
       <c r="C226" t="n">
         <v>28.94000053405762</v>
@@ -6495,11 +6507,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>24.71137809753418</v>
+        <v>24.71138000488281</v>
       </c>
       <c r="C227" t="n">
         <v>28.29999923706055</v>
@@ -6522,11 +6534,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>23.24188613891602</v>
+        <v>23.24188804626465</v>
       </c>
       <c r="C228" t="n">
         <v>26.20999908447266</v>
@@ -6551,7 +6563,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6580,7 +6592,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6609,7 +6621,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>22.84189414978027</v>
+        <v>22.84189605712891</v>
       </c>
       <c r="C232" t="n">
         <v>25.34000015258789</v>
@@ -6667,11 +6679,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>22.00357818603516</v>
+        <v>22.00357627868652</v>
       </c>
       <c r="C233" t="n">
         <v>24.40999984741211</v>
@@ -6696,11 +6708,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>21.57822227478027</v>
+        <v>21.57822036743164</v>
       </c>
       <c r="C234" t="n">
         <v>23.48999977111816</v>
@@ -6725,11 +6737,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>22.26717948913574</v>
+        <v>22.26718139648438</v>
       </c>
       <c r="C235" t="n">
         <v>24.23999977111816</v>
@@ -6754,7 +6766,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6783,11 +6795,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>23.1373291015625</v>
+        <v>23.13732719421387</v>
       </c>
       <c r="C237" t="n">
         <v>24.76000022888184</v>
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6841,7 +6853,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6870,11 +6882,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>24.47664070129395</v>
+        <v>24.47664260864258</v>
       </c>
       <c r="C240" t="n">
         <v>25.73999977111816</v>
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6928,7 +6940,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6957,7 +6969,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6986,7 +6998,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7102,7 +7114,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7131,7 +7143,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7160,32 +7172,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>28.18000030517578</v>
+        <v>28.40999984741211</v>
       </c>
       <c r="C250" t="n">
-        <v>28.18000030517578</v>
+        <v>28.40999984741211</v>
       </c>
       <c r="D250" t="n">
-        <v>536421600</v>
+        <v>571180900</v>
       </c>
       <c r="E250" t="n">
         <v>0.7600000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>37.07894776996812</v>
+        <v>37.38157874659488</v>
       </c>
       <c r="G250" t="n">
         <v>5699673589</v>
       </c>
       <c r="H250" t="n">
-        <v>160616803477.4223</v>
+        <v>161927725793.7888</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09411444210336165</v>
+        <v>0.1002129141399153</v>
       </c>
     </row>
   </sheetData>
@@ -7217,75 +7229,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39628</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39719</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39901</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40311</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39902</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39992</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39993</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40083</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40272</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40311</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7531,13 +7543,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40273</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40363</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40402</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7573,13 +7585,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40364</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40454</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40494</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7615,13 +7627,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40455</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7648,7 +7660,7 @@
       <c r="I10" t="n">
         <v>0.967741935483871</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7661,13 +7673,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40636</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7694,7 +7706,7 @@
       <c r="I11" t="n">
         <v>0.9962049335863377</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="K11" t="n">
@@ -7707,13 +7719,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40637</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40727</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40766</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7740,7 +7752,7 @@
       <c r="I12" t="n">
         <v>1.015180265654649</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40766</v>
       </c>
       <c r="K12" t="n">
@@ -7753,13 +7765,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40728</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40818</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40857</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7786,7 +7798,7 @@
       <c r="I13" t="n">
         <v>1.366223908918406</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40857</v>
       </c>
       <c r="K13" t="n">
@@ -7799,13 +7811,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40819</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7832,7 +7844,7 @@
       <c r="I14" t="n">
         <v>1.204933586337761</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K14" t="n">
@@ -7845,13 +7857,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7878,7 +7890,7 @@
       <c r="I15" t="n">
         <v>1.166982922201139</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="K15" t="n">
@@ -7891,13 +7903,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41001</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7924,7 +7936,7 @@
       <c r="I16" t="n">
         <v>1.261859582542694</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="K16" t="n">
@@ -7937,13 +7949,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41092</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7970,7 +7982,7 @@
       <c r="I17" t="n">
         <v>1.214421252371916</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="K17" t="n">
@@ -7983,13 +7995,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8016,7 +8028,7 @@
       <c r="I18" t="n">
         <v>1.840607210626186</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K18" t="n">
@@ -8029,13 +8041,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8062,7 +8074,7 @@
       <c r="I19" t="n">
         <v>1.973434535104364</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="K19" t="n">
@@ -8075,13 +8087,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41495</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8108,7 +8120,7 @@
       <c r="I20" t="n">
         <v>3.444022770398482</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41495</v>
       </c>
       <c r="K20" t="n">
@@ -8121,13 +8133,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8154,7 +8166,7 @@
       <c r="I21" t="n">
         <v>3.40607210626186</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="K21" t="n">
@@ -8167,13 +8179,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8200,7 +8212,7 @@
       <c r="I22" t="n">
         <v>3.026565464895635</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K22" t="n">
@@ -8213,13 +8225,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8246,7 +8258,7 @@
       <c r="I23" t="n">
         <v>3.007590132827324</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K23" t="n">
@@ -8259,13 +8271,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8292,7 +8304,7 @@
       <c r="I24" t="n">
         <v>1.555977229601518</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="K24" t="n">
@@ -8305,13 +8317,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8338,7 +8350,7 @@
       <c r="I25" t="n">
         <v>1.584440227703985</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K25" t="n">
@@ -8351,13 +8363,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41911</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8384,7 +8396,7 @@
       <c r="I26" t="n">
         <v>1.347248576850095</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K26" t="n">
@@ -8397,13 +8409,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8430,7 +8442,7 @@
       <c r="I27" t="n">
         <v>1.366223908918406</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K27" t="n">
@@ -8443,13 +8455,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42093</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8476,7 +8488,7 @@
       <c r="I28" t="n">
         <v>1.337760910815939</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K28" t="n">
@@ -8489,13 +8501,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42184</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8522,7 +8534,7 @@
       <c r="I29" t="n">
         <v>1.261859582542694</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K29" t="n">
@@ -8535,13 +8547,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42275</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8568,7 +8580,7 @@
       <c r="I30" t="n">
         <v>1.053130929791271</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="K30" t="n">
@@ -8581,13 +8593,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42463</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42502</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8614,7 +8626,7 @@
       <c r="I31" t="n">
         <v>1.157495256166983</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42502</v>
       </c>
       <c r="K31" t="n">
@@ -8627,13 +8639,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42464</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42554</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42593</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8660,7 +8672,7 @@
       <c r="I32" t="n">
         <v>1.072106261859583</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42593</v>
       </c>
       <c r="K32" t="n">
@@ -8673,13 +8685,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42555</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42645</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42684</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8706,7 +8718,7 @@
       <c r="I33" t="n">
         <v>0.94876660341556</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42684</v>
       </c>
       <c r="K33" t="n">
@@ -8719,13 +8731,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42646</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8752,7 +8764,7 @@
       <c r="I34" t="n">
         <v>1.110056925996205</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K34" t="n">
@@ -8765,13 +8777,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42866</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8798,7 +8810,7 @@
       <c r="I35" t="n">
         <v>1.129032258064516</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42866</v>
       </c>
       <c r="K35" t="n">
@@ -8811,13 +8823,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42828</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42957</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8844,7 +8856,7 @@
       <c r="I36" t="n">
         <v>1.299810246679317</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42957</v>
       </c>
       <c r="K36" t="n">
@@ -8857,13 +8869,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42919</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43048</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8890,7 +8902,7 @@
       <c r="I37" t="n">
         <v>1.546489563567362</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43048</v>
       </c>
       <c r="K37" t="n">
@@ -8903,13 +8915,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43010</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8936,7 +8948,7 @@
       <c r="I38" t="n">
         <v>3.33965844402277</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K38" t="n">
@@ -8949,13 +8961,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43230</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8982,7 +8994,7 @@
       <c r="I39" t="n">
         <v>3.415559772296015</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43230</v>
       </c>
       <c r="K39" t="n">
@@ -8995,13 +9007,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43192</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43321</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9028,7 +9040,7 @@
       <c r="I40" t="n">
         <v>3.548387096774193</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43321</v>
       </c>
       <c r="K40" t="n">
@@ -9041,13 +9053,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43283</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9074,7 +9086,7 @@
       <c r="I41" t="n">
         <v>3.757115749525616</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="K41" t="n">
@@ -9087,13 +9099,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9120,7 +9132,7 @@
       <c r="I42" t="n">
         <v>1.774193548387097</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="K42" t="n">
@@ -9133,13 +9145,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9166,7 +9178,7 @@
       <c r="I43" t="n">
         <v>1.859582542694497</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K43" t="n">
@@ -9179,13 +9191,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9212,7 +9224,7 @@
       <c r="I44" t="n">
         <v>2.087286527514232</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="K44" t="n">
@@ -9225,13 +9237,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9258,7 +9270,7 @@
       <c r="I45" t="n">
         <v>2.722960151802657</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="K45" t="n">
@@ -9271,13 +9283,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9304,7 +9316,7 @@
       <c r="I46" t="n">
         <v>2.722960151802657</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K46" t="n">
@@ -9317,13 +9329,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9350,7 +9362,7 @@
       <c r="I47" t="n">
         <v>2.656546489563568</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K47" t="n">
@@ -9363,13 +9375,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43920</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9396,7 +9408,7 @@
       <c r="I48" t="n">
         <v>2.390891840607211</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K48" t="n">
@@ -9409,13 +9421,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44011</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9442,7 +9454,7 @@
       <c r="I49" t="n">
         <v>1.470588235294118</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K49" t="n">
@@ -9455,13 +9467,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44102</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9488,7 +9500,7 @@
       <c r="I50" t="n">
         <v>1.71</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K50" t="n">
@@ -9501,13 +9513,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44290</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44329</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9534,7 +9546,7 @@
       <c r="I51" t="n">
         <v>1.991252371916509</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44329</v>
       </c>
       <c r="K51" t="n">
@@ -9547,13 +9559,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44291</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44381</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9580,7 +9592,7 @@
       <c r="I52" t="n">
         <v>2.392504743833017</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="K52" t="n">
@@ -9593,13 +9605,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44382</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44472</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9626,7 +9638,7 @@
       <c r="I53" t="n">
         <v>3.442485768500949</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="K53" t="n">
@@ -9639,13 +9651,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44473</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9672,7 +9684,7 @@
       <c r="I54" t="n">
         <v>3.85</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K54" t="n">
@@ -9685,13 +9697,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44654</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44692</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9718,7 +9730,7 @@
       <c r="I55" t="n">
         <v>4.36</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44692</v>
       </c>
       <c r="K55" t="n">
@@ -9731,13 +9743,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44655</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44745</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44783</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9764,7 +9776,7 @@
       <c r="I56" t="n">
         <v>5.11</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44783</v>
       </c>
       <c r="K56" t="n">
@@ -9777,13 +9789,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44746</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44836</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9810,7 +9822,7 @@
       <c r="I57" t="n">
         <v>5.2</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="K57" t="n">
@@ -9823,13 +9835,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44837</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9856,7 +9868,7 @@
       <c r="I58" t="n">
         <v>5.469999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K58" t="n">
@@ -9869,13 +9881,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9902,7 +9914,7 @@
       <c r="I59" t="n">
         <v>5.07</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="K59" t="n">
@@ -9915,13 +9927,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45019</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9948,7 +9960,7 @@
       <c r="I60" t="n">
         <v>3.75</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="K60" t="n">
@@ -9961,13 +9973,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9994,7 +10006,7 @@
       <c r="I61" t="n">
         <v>1.819999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="K61" t="n">
@@ -10007,13 +10019,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10040,7 +10052,7 @@
       <c r="I62" t="n">
         <v>0.37</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K62" t="n">
@@ -10053,13 +10065,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10086,7 +10098,7 @@
       <c r="I63" t="n">
         <v>-0.04999999999999993</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K63" t="n">
@@ -10099,13 +10111,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10132,7 +10144,7 @@
       <c r="I64" t="n">
         <v>-0.4499999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K64" t="n">
@@ -10145,13 +10157,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10178,7 +10190,7 @@
       <c r="I65" t="n">
         <v>0.7500000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="K65" t="n">
@@ -10191,13 +10203,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10224,7 +10236,7 @@
       <c r="I66" t="n">
         <v>1.41</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K66" t="n">
@@ -10237,13 +10249,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10270,7 +10282,7 @@
       <c r="I67" t="n">
         <v>1.38</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="K67" t="n">
@@ -10283,13 +10295,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10316,7 +10328,7 @@
       <c r="I68" t="n">
         <v>1.88</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K68" t="n">
@@ -10329,13 +10341,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10362,7 +10374,7 @@
       <c r="I69" t="n">
         <v>1.72</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K69" t="n">
@@ -10375,13 +10387,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45929</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10408,7 +10420,7 @@
       <c r="I70" t="n">
         <v>1.36</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="K70" t="n">
@@ -10421,13 +10433,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10454,7 +10466,7 @@
       <c r="I71" t="n">
         <v>1.31</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K71" t="n">
@@ -10467,13 +10479,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46111</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46201</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10500,7 +10512,7 @@
       <c r="I72" t="n">
         <v>0.7600000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K72" t="n">
@@ -10537,52 +10549,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40029</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="C2" t="n">
@@ -10611,10 +10623,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40119</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10643,10 +10655,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40227</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10675,10 +10687,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40308</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40311</v>
       </c>
       <c r="C5" t="n">
@@ -10707,10 +10719,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40399</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40402</v>
       </c>
       <c r="C6" t="n">
@@ -10739,10 +10751,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40490</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40494</v>
       </c>
       <c r="C7" t="n">
@@ -10771,10 +10783,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40596</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10803,10 +10815,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40672</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="C9" t="n">
@@ -10835,10 +10847,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40763</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40766</v>
       </c>
       <c r="C10" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40854</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40857</v>
       </c>
       <c r="C11" t="n">
@@ -10899,10 +10911,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40960</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C12" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41036</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="C13" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41127</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="C14" t="n">
@@ -10995,10 +11007,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41218</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="C15" t="n">
@@ -11027,10 +11039,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41326</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41400</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="C17" t="n">
@@ -11091,10 +11103,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41491</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41495</v>
       </c>
       <c r="C18" t="n">
@@ -11123,10 +11135,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41582</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="C19" t="n">
@@ -11155,10 +11167,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41691</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C20" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41764</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C21" t="n">
@@ -11219,10 +11231,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41855</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C22" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41946</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C23" t="n">
@@ -11283,10 +11295,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42055</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C24" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42128</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C25" t="n">
@@ -11347,10 +11359,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42219</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C26" t="n">
@@ -11379,10 +11391,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42310</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C27" t="n">
@@ -11411,10 +11423,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42425</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="C28" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42499</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42502</v>
       </c>
       <c r="C29" t="n">
@@ -11475,10 +11487,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42590</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42593</v>
       </c>
       <c r="C30" t="n">
@@ -11507,10 +11519,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42681</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42684</v>
       </c>
       <c r="C31" t="n">
@@ -11539,10 +11551,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42787</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42863</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42866</v>
       </c>
       <c r="C33" t="n">
@@ -11603,10 +11615,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42954</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42957</v>
       </c>
       <c r="C34" t="n">
@@ -11635,10 +11647,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43045</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43048</v>
       </c>
       <c r="C35" t="n">
@@ -11667,10 +11679,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43151</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C36" t="n">
@@ -11699,10 +11711,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43227</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43230</v>
       </c>
       <c r="C37" t="n">
@@ -11731,10 +11743,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43318</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43321</v>
       </c>
       <c r="C38" t="n">
@@ -11763,10 +11775,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43409</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="C39" t="n">
@@ -11795,10 +11807,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43522</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="C40" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43591</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C41" t="n">
@@ -11859,10 +11871,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43682</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="C42" t="n">
@@ -11891,10 +11903,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43773</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="C43" t="n">
@@ -11923,10 +11935,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43886</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C44" t="n">
@@ -11955,10 +11967,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43955</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C45" t="n">
@@ -11987,10 +11999,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44046</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C46" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44137</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C47" t="n">
@@ -12051,10 +12063,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44250</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C48" t="n">
@@ -12083,10 +12095,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44326</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44329</v>
       </c>
       <c r="C49" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44417</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="C50" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44508</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="C51" t="n">
@@ -12179,10 +12191,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44614</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C52" t="n">
@@ -12211,10 +12223,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44687</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44692</v>
       </c>
       <c r="C53" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44778</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44783</v>
       </c>
       <c r="C54" t="n">
@@ -12275,10 +12287,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44869</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="C55" t="n">
@@ -12307,10 +12319,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44978</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C56" t="n">
@@ -12339,10 +12351,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45051</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="C57" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45142</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="C58" t="n">
@@ -12403,10 +12415,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45233</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="C59" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C60" t="n">
@@ -12467,10 +12479,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45415</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C61" t="n">
@@ -12499,10 +12511,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C62" t="n">
@@ -12531,10 +12543,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45595</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="C63" t="n">
@@ -12563,10 +12575,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45708</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C64" t="n">
@@ -12595,10 +12607,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="C65" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45868</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C66" t="n">
@@ -12659,10 +12671,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45959</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C67" t="n">
@@ -12691,10 +12703,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46072</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C68" t="n">
@@ -12723,10 +12735,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C69" t="n">
@@ -12755,10 +12767,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46232</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C70" t="n">
@@ -12805,12 +12817,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PFE.xlsx
+++ b/salidas/empresas/PFE.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>10.18790912628174</v>
+        <v>10.187912940979</v>
       </c>
       <c r="C3" t="n">
         <v>24.84819793701172</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>9.693875312805176</v>
+        <v>9.693882942199707</v>
       </c>
       <c r="C4" t="n">
         <v>23.64326477050781</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>9.853368759155273</v>
+        <v>9.853364944458008</v>
       </c>
       <c r="C5" t="n">
         <v>24.03225708007812</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>9.291153907775879</v>
+        <v>9.291156768798828</v>
       </c>
       <c r="C6" t="n">
         <v>22.44781875610352</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>9.216541290283203</v>
+        <v>9.21653938293457</v>
       </c>
       <c r="C7" t="n">
         <v>22.26755142211914</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>10.20612812042236</v>
+        <v>10.206130027771</v>
       </c>
       <c r="C8" t="n">
         <v>24.65844345092773</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>10.92287254333496</v>
+        <v>10.92286968231201</v>
       </c>
       <c r="C9" t="n">
         <v>26.14800834655762</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.23993110656738</v>
+        <v>11.23993015289307</v>
       </c>
       <c r="C10" t="n">
         <v>26.90702056884766</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>10.99179363250732</v>
+        <v>10.99179267883301</v>
       </c>
       <c r="C12" t="n">
         <v>26.08159446716309</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>10.35603809356689</v>
+        <v>10.356032371521</v>
       </c>
       <c r="C13" t="n">
         <v>24.57305526733398</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>10.49198627471924</v>
+        <v>10.49198722839355</v>
       </c>
       <c r="C14" t="n">
         <v>24.8956356048584</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>10.08923244476318</v>
+        <v>10.08923149108887</v>
       </c>
       <c r="C15" t="n">
         <v>23.68121337890625</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.2104959487915</v>
+        <v>10.21049880981445</v>
       </c>
       <c r="C16" t="n">
         <v>23.96584320068359</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.69555473327637</v>
+        <v>10.69555377960205</v>
       </c>
       <c r="C17" t="n">
         <v>25.1043643951416</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>11.23098468780518</v>
+        <v>11.23098373413086</v>
       </c>
       <c r="C18" t="n">
         <v>26.08159446716309</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>10.44657325744629</v>
+        <v>10.44657611846924</v>
       </c>
       <c r="C19" t="n">
         <v>24.25996208190918</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>9.604966163635254</v>
+        <v>9.604963302612305</v>
       </c>
       <c r="C20" t="n">
         <v>22.30550384521484</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>10.27065277099609</v>
+        <v>10.27064609527588</v>
       </c>
       <c r="C21" t="n">
         <v>23.56736183166504</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>10.1011266708374</v>
+        <v>10.10112285614014</v>
       </c>
       <c r="C22" t="n">
         <v>23.17836761474609</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>9.513511657714844</v>
+        <v>9.513515472412109</v>
       </c>
       <c r="C25" t="n">
         <v>21.56546592712402</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>9.77719783782959</v>
+        <v>9.777195930480957</v>
       </c>
       <c r="C26" t="n">
         <v>22.16318893432617</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>8.535895347595215</v>
+        <v>8.535896301269531</v>
       </c>
       <c r="C29" t="n">
         <v>19.07969665527344</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>8.34837818145752</v>
+        <v>8.348381042480469</v>
       </c>
       <c r="C30" t="n">
         <v>18.36812019348145</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>7.53337574005127</v>
+        <v>7.533375263214111</v>
       </c>
       <c r="C31" t="n">
         <v>16.57495307922363</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>8.376568794250488</v>
+        <v>8.37657356262207</v>
       </c>
       <c r="C33" t="n">
         <v>18.13092994689941</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>7.762901306152344</v>
+        <v>7.762901782989502</v>
       </c>
       <c r="C35" t="n">
         <v>16.80265617370605</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>7.329229831695557</v>
+        <v>7.32922887802124</v>
       </c>
       <c r="C36" t="n">
         <v>15.58823490142822</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>7.900221347808838</v>
+        <v>7.900225639343262</v>
       </c>
       <c r="C37" t="n">
         <v>16.80265617370605</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.503966808319092</v>
+        <v>6.503965854644775</v>
       </c>
       <c r="C38" t="n">
         <v>13.83301734924316</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.609440803527832</v>
+        <v>5.609439849853516</v>
       </c>
       <c r="C39" t="n">
         <v>11.67931747436523</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>6.20638370513916</v>
+        <v>6.206380367279053</v>
       </c>
       <c r="C40" t="n">
         <v>12.92220115661621</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>7.000235080718994</v>
+        <v>7.000237464904785</v>
       </c>
       <c r="C42" t="n">
         <v>14.41176509857178</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>6.912675380706787</v>
+        <v>6.912676334381104</v>
       </c>
       <c r="C43" t="n">
         <v>14.23149871826172</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>7.341259002685547</v>
+        <v>7.341262340545654</v>
       </c>
       <c r="C44" t="n">
         <v>15.11385154724121</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>7.773512840270996</v>
+        <v>7.773509979248047</v>
       </c>
       <c r="C45" t="n">
         <v>15.84440231323242</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>7.703690528869629</v>
+        <v>7.703688621520996</v>
       </c>
       <c r="C46" t="n">
         <v>15.70208740234375</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>7.927116870880127</v>
+        <v>7.927118301391602</v>
       </c>
       <c r="C47" t="n">
         <v>16.15749549865723</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>8.538652420043945</v>
+        <v>8.53864860534668</v>
       </c>
       <c r="C48" t="n">
         <v>17.23908805847168</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.548052787780762</v>
+        <v>8.548051834106445</v>
       </c>
       <c r="C49" t="n">
         <v>17.25806427001953</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>8.768918037414551</v>
+        <v>8.768915176391602</v>
       </c>
       <c r="C50" t="n">
         <v>17.7039852142334</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.325183868408203</v>
+        <v>8.325179100036621</v>
       </c>
       <c r="C51" t="n">
         <v>16.65085411071777</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>7.931455135345459</v>
+        <v>7.931454181671143</v>
       </c>
       <c r="C53" t="n">
         <v>15.86337757110596</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.300779342651367</v>
+        <v>7.300781726837158</v>
       </c>
       <c r="C54" t="n">
         <v>14.44971466064453</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>6.835793972015381</v>
+        <v>6.835794925689697</v>
       </c>
       <c r="C55" t="n">
         <v>13.52941226959229</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>7.190529823303223</v>
+        <v>7.190526962280273</v>
       </c>
       <c r="C56" t="n">
         <v>14.23149871826172</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>7.711703300476074</v>
+        <v>7.711702823638916</v>
       </c>
       <c r="C57" t="n">
         <v>15.09487724304199</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>8.443610191345215</v>
+        <v>8.443612098693848</v>
       </c>
       <c r="C59" t="n">
         <v>16.52751350402832</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>7.982423782348633</v>
+        <v>7.982426166534424</v>
       </c>
       <c r="C60" t="n">
         <v>15.4648962020874</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>8.574986457824707</v>
+        <v>8.574983596801758</v>
       </c>
       <c r="C61" t="n">
         <v>16.6129035949707</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>8.922687530517578</v>
+        <v>8.922684669494629</v>
       </c>
       <c r="C62" t="n">
         <v>17.28652763366699</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>9.521273612976074</v>
+        <v>9.521276473999023</v>
       </c>
       <c r="C63" t="n">
         <v>18.25426864624023</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>10.37739658355713</v>
+        <v>10.37739753723145</v>
       </c>
       <c r="C65" t="n">
         <v>19.8956356048584</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.71769332885742</v>
+        <v>10.71769714355469</v>
       </c>
       <c r="C66" t="n">
         <v>20.35104370117188</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.29298400878906</v>
+        <v>10.29298305511475</v>
       </c>
       <c r="C67" t="n">
         <v>19.54459190368652</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>9.618444442749023</v>
+        <v>9.618447303771973</v>
       </c>
       <c r="C68" t="n">
         <v>18.26375770568848</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>9.58925724029541</v>
+        <v>9.589258193969727</v>
       </c>
       <c r="C69" t="n">
         <v>18.00758934020996</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>8.932462692260742</v>
+        <v>8.932463645935059</v>
       </c>
       <c r="C70" t="n">
         <v>16.77419471740723</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>9.730728149414062</v>
+        <v>9.730725288391113</v>
       </c>
       <c r="C71" t="n">
         <v>18.27324485778809</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>10.24202632904053</v>
+        <v>10.24202346801758</v>
       </c>
       <c r="C72" t="n">
         <v>19.04174613952637</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>10.92073917388916</v>
+        <v>10.92074489593506</v>
       </c>
       <c r="C74" t="n">
         <v>20.30360412597656</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>10.89496326446533</v>
+        <v>10.89496517181396</v>
       </c>
       <c r="C75" t="n">
         <v>20.04743766784668</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>11.6786994934082</v>
+        <v>11.67870044708252</v>
       </c>
       <c r="C76" t="n">
         <v>21.48956489562988</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>11.80759906768799</v>
+        <v>11.80760669708252</v>
       </c>
       <c r="C77" t="n">
         <v>21.72675514221191</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>11.38826942443848</v>
+        <v>11.38826847076416</v>
       </c>
       <c r="C78" t="n">
         <v>20.74952507019043</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>11.97668743133545</v>
+        <v>11.97668838500977</v>
       </c>
       <c r="C79" t="n">
         <v>21.82163238525391</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>12.53926467895508</v>
+        <v>12.53926277160645</v>
       </c>
       <c r="C81" t="n">
         <v>22.63757133483887</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>13.05954456329346</v>
+        <v>13.05954170227051</v>
       </c>
       <c r="C82" t="n">
         <v>23.57685089111328</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>13.0700569152832</v>
+        <v>13.07005596160889</v>
       </c>
       <c r="C83" t="n">
         <v>23.5958251953125</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>13.26700401306152</v>
+        <v>13.26700210571289</v>
       </c>
       <c r="C84" t="n">
         <v>23.73814010620117</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>13.29882144927979</v>
+        <v>13.2988224029541</v>
       </c>
       <c r="C85" t="n">
         <v>23.79506683349609</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>14.59181499481201</v>
+        <v>14.59181022644043</v>
       </c>
       <c r="C86" t="n">
         <v>25.88235282897949</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>14.63995265960693</v>
+        <v>14.6399450302124</v>
       </c>
       <c r="C87" t="n">
         <v>25.96774291992188</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>15.43693542480469</v>
+        <v>15.43693733215332</v>
       </c>
       <c r="C88" t="n">
         <v>27.38140487670898</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>15.5492639541626</v>
+        <v>15.54926586151123</v>
       </c>
       <c r="C89" t="n">
         <v>27.58064460754395</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>14.68648719787598</v>
+        <v>14.68648529052734</v>
       </c>
       <c r="C90" t="n">
         <v>25.83491516113281</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>15.10717582702637</v>
+        <v>15.10717487335205</v>
       </c>
       <c r="C91" t="n">
         <v>26.57495307922363</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>15.89374446868896</v>
+        <v>15.89374256134033</v>
       </c>
       <c r="C92" t="n">
         <v>27.73244857788086</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>15.33912467956543</v>
+        <v>15.3391227722168</v>
       </c>
       <c r="C93" t="n">
         <v>26.76470565795898</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>15.62187385559082</v>
+        <v>15.6218729019165</v>
       </c>
       <c r="C94" t="n">
         <v>27.25806427001953</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>16.68761253356934</v>
+        <v>16.68762016296387</v>
       </c>
       <c r="C95" t="n">
         <v>29.11764717102051</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>17.38669013977051</v>
+        <v>17.38668441772461</v>
       </c>
       <c r="C96" t="n">
         <v>30.1043643951416</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65790748596191</v>
+        <v>16.65790176391602</v>
       </c>
       <c r="C98" t="n">
         <v>28.84250450134277</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>17.74163055419922</v>
+        <v>17.74162864685059</v>
       </c>
       <c r="C99" t="n">
         <v>30.46489524841309</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.74715423583984</v>
+        <v>17.74715232849121</v>
       </c>
       <c r="C100" t="n">
         <v>30.4743824005127</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>17.28303146362305</v>
+        <v>17.28303527832031</v>
       </c>
       <c r="C101" t="n">
         <v>29.67741966247559</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>16.54515647888184</v>
+        <v>16.5451545715332</v>
       </c>
       <c r="C103" t="n">
         <v>28.15939331054688</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>16.52803611755371</v>
+        <v>16.52803993225098</v>
       </c>
       <c r="C105" t="n">
         <v>27.88425064086914</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>16.62926483154297</v>
+        <v>16.62926864624023</v>
       </c>
       <c r="C106" t="n">
         <v>28.05502891540527</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>16.84296607971191</v>
+        <v>16.84296417236328</v>
       </c>
       <c r="C107" t="n">
         <v>28.41555976867676</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>17.66952705383301</v>
+        <v>17.66952896118164</v>
       </c>
       <c r="C108" t="n">
         <v>29.55407905578613</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>17.66952705383301</v>
+        <v>17.66952896118164</v>
       </c>
       <c r="C109" t="n">
         <v>29.55407905578613</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>17.72625541687012</v>
+        <v>17.72625350952148</v>
       </c>
       <c r="C110" t="n">
         <v>29.64895629882812</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>19.63942337036133</v>
+        <v>19.63941764831543</v>
       </c>
       <c r="C111" t="n">
         <v>32.56166839599609</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.90837478637695</v>
+        <v>19.90837860107422</v>
       </c>
       <c r="C112" t="n">
         <v>33.00759124755859</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>19.41625022888184</v>
+        <v>19.41624450683594</v>
       </c>
       <c r="C113" t="n">
         <v>32.191650390625</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>19.34610748291016</v>
+        <v>19.34610939025879</v>
       </c>
       <c r="C115" t="n">
         <v>31.81214332580566</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>20.80586433410645</v>
+        <v>20.80586242675781</v>
       </c>
       <c r="C116" t="n">
         <v>34.2125244140625</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>18.26453971862793</v>
+        <v>18.2645435333252</v>
       </c>
       <c r="C118" t="n">
         <v>29.80075836181641</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>19.20916175842285</v>
+        <v>19.20916557312012</v>
       </c>
       <c r="C120" t="n">
         <v>31.0910816192627</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>17.87267303466797</v>
+        <v>17.87267112731934</v>
       </c>
       <c r="C122" t="n">
         <v>28.92789459228516</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>17.54909324645996</v>
+        <v>17.54909896850586</v>
       </c>
       <c r="C124" t="n">
         <v>28.1214427947998</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>19.36676025390625</v>
+        <v>19.36676788330078</v>
       </c>
       <c r="C125" t="n">
         <v>31.03415679931641</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>20.72897529602051</v>
+        <v>20.72897720336914</v>
       </c>
       <c r="C126" t="n">
         <v>32.92219924926758</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>22.03723335266113</v>
+        <v>22.0372371673584</v>
       </c>
       <c r="C128" t="n">
         <v>35</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>20.96152305603027</v>
+        <v>20.96152687072754</v>
       </c>
       <c r="C129" t="n">
         <v>33.0170783996582</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>19.10028648376465</v>
+        <v>19.10028266906738</v>
       </c>
       <c r="C131" t="n">
         <v>30.08538818359375</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>19.55237197875977</v>
+        <v>19.5523681640625</v>
       </c>
       <c r="C132" t="n">
         <v>30.49335861206055</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>19.75921058654785</v>
+        <v>19.75921249389648</v>
       </c>
       <c r="C133" t="n">
         <v>30.81593894958496</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>19.30294990539551</v>
+        <v>19.30294227600098</v>
       </c>
       <c r="C134" t="n">
         <v>30.1043643951416</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>20.96836471557617</v>
+        <v>20.9683723449707</v>
       </c>
       <c r="C135" t="n">
         <v>32.37191772460938</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>21.023681640625</v>
+        <v>21.02367973327637</v>
       </c>
       <c r="C136" t="n">
         <v>32.45730590820312</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>20.25920104980469</v>
+        <v>20.25919914245605</v>
       </c>
       <c r="C138" t="n">
         <v>30.97723007202148</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>20.84247016906738</v>
+        <v>20.84246826171875</v>
       </c>
       <c r="C139" t="n">
         <v>31.86907005310059</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>20.57566452026367</v>
+        <v>20.57565689086914</v>
       </c>
       <c r="C140" t="n">
         <v>31.46110153198242</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>22.90126991271973</v>
+        <v>22.90126800537109</v>
       </c>
       <c r="C145" t="n">
         <v>34.36432647705078</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>23.41974449157715</v>
+        <v>23.41974067687988</v>
       </c>
       <c r="C146" t="n">
         <v>35.14231491088867</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>23.17086791992188</v>
+        <v>23.17087364196777</v>
       </c>
       <c r="C147" t="n">
         <v>34.44971466064453</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>22.64759254455566</v>
+        <v>22.6475944519043</v>
       </c>
       <c r="C148" t="n">
         <v>33.67172622680664</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>23.36231231689453</v>
+        <v>23.36230850219727</v>
       </c>
       <c r="C149" t="n">
         <v>34.73434448242188</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>23.15220069885254</v>
+        <v>23.15219497680664</v>
       </c>
       <c r="C150" t="n">
         <v>34.08918380737305</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>23.37773132324219</v>
+        <v>23.37772941589355</v>
       </c>
       <c r="C151" t="n">
         <v>34.4212532043457</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>25.72967529296875</v>
+        <v>25.72967720031738</v>
       </c>
       <c r="C152" t="n">
         <v>37.88425064086914</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>26.98202896118164</v>
+        <v>26.98203086853027</v>
       </c>
       <c r="C153" t="n">
         <v>39.39278793334961</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>28.63916015625</v>
+        <v>28.6391658782959</v>
       </c>
       <c r="C154" t="n">
         <v>41.8121452331543</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>27.9828052520752</v>
+        <v>27.98280715942383</v>
       </c>
       <c r="C155" t="n">
         <v>40.85388946533203</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>28.58511734008789</v>
+        <v>28.58512878417969</v>
       </c>
       <c r="C157" t="n">
         <v>41.41366195678711</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>28.04206848144531</v>
+        <v>28.04206657409668</v>
       </c>
       <c r="C158" t="n">
         <v>40.27514266967773</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>28.6365966796875</v>
+        <v>28.63658714294434</v>
       </c>
       <c r="C159" t="n">
         <v>41.12903213500977</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>28.05527114868164</v>
+        <v>28.05527496337891</v>
       </c>
       <c r="C160" t="n">
         <v>40.29411697387695</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>26.82657432556152</v>
+        <v>26.82657623291016</v>
       </c>
       <c r="C161" t="n">
         <v>38.52941131591797</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>27.67097091674805</v>
+        <v>27.67097282409668</v>
       </c>
       <c r="C162" t="n">
         <v>39.39278793334961</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>28.87057876586914</v>
+        <v>28.87058639526367</v>
       </c>
       <c r="C163" t="n">
         <v>41.10057067871094</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>25.88489151000977</v>
+        <v>25.88489723205566</v>
       </c>
       <c r="C164" t="n">
         <v>36.85009384155273</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>23.91392135620117</v>
+        <v>23.91392707824707</v>
       </c>
       <c r="C165" t="n">
         <v>33.72865295410156</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>24.16954803466797</v>
+        <v>24.1695499420166</v>
       </c>
       <c r="C166" t="n">
         <v>34.08918380737305</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>25.8108959197998</v>
+        <v>25.81089973449707</v>
       </c>
       <c r="C167" t="n">
         <v>36.4041748046875</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>26.61048698425293</v>
+        <v>26.61049270629883</v>
       </c>
       <c r="C169" t="n">
         <v>37.17267608642578</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>25.55123138427734</v>
+        <v>25.55123329162598</v>
       </c>
       <c r="C170" t="n">
         <v>35.33206939697266</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>22.93024063110352</v>
+        <v>22.93024444580078</v>
       </c>
       <c r="C171" t="n">
         <v>31.7077808380127</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>22.39506912231445</v>
+        <v>22.39506721496582</v>
       </c>
       <c r="C172" t="n">
         <v>30.96774291992188</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>26.92575645446777</v>
+        <v>26.92576217651367</v>
       </c>
       <c r="C176" t="n">
         <v>36.50853729248047</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>26.44294738769531</v>
+        <v>26.44294929504395</v>
       </c>
       <c r="C177" t="n">
         <v>35.85388946533203</v>
@@ -5129,7 +5129,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>24.82655715942383</v>
+        <v>24.82656288146973</v>
       </c>
       <c r="C179" t="n">
         <v>33.66223907470703</v>
@@ -5158,7 +5158,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>28.54494285583496</v>
+        <v>28.54494857788086</v>
       </c>
       <c r="C180" t="n">
         <v>38.31000137329102</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>27.04024505615234</v>
+        <v>27.04024314880371</v>
       </c>
       <c r="C182" t="n">
         <v>35.90000152587891</v>
@@ -5274,7 +5274,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>27.28879737854004</v>
+        <v>27.28879928588867</v>
       </c>
       <c r="C184" t="n">
         <v>36.22999954223633</v>
@@ -5303,7 +5303,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>29.1115608215332</v>
+        <v>29.11157035827637</v>
       </c>
       <c r="C185" t="n">
         <v>38.65000152587891</v>
@@ -5332,7 +5332,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>29.45927238464355</v>
+        <v>29.45926666259766</v>
       </c>
       <c r="C186" t="n">
         <v>38.72999954223633</v>
@@ -5361,7 +5361,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>29.78634071350098</v>
+        <v>29.78634452819824</v>
       </c>
       <c r="C187" t="n">
         <v>39.15999984741211</v>
@@ -5390,7 +5390,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>32.85758209228516</v>
+        <v>32.85757827758789</v>
       </c>
       <c r="C188" t="n">
         <v>42.81000137329102</v>
@@ -5419,7 +5419,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>35.35969161987305</v>
+        <v>35.35968780517578</v>
       </c>
       <c r="C189" t="n">
         <v>46.06999969482422</v>
@@ -5448,7 +5448,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>33.01107406616211</v>
+        <v>33.01108169555664</v>
       </c>
       <c r="C190" t="n">
         <v>43.0099983215332</v>
@@ -5535,7 +5535,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>45.71992874145508</v>
+        <v>45.71994018554688</v>
       </c>
       <c r="C193" t="n">
         <v>59.04999923706055</v>
@@ -5564,7 +5564,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>41.1058349609375</v>
+        <v>41.10584259033203</v>
       </c>
       <c r="C194" t="n">
         <v>52.68999862670898</v>
@@ -5593,7 +5593,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>36.61999893188477</v>
+        <v>36.62000274658203</v>
       </c>
       <c r="C195" t="n">
         <v>46.93999862670898</v>
@@ -5622,7 +5622,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>40.38810348510742</v>
+        <v>40.38810729980469</v>
       </c>
       <c r="C196" t="n">
         <v>51.77000045776367</v>
@@ -5651,7 +5651,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>38.28170776367188</v>
+        <v>38.28171157836914</v>
       </c>
       <c r="C197" t="n">
         <v>49.06999969482422</v>
@@ -5709,7 +5709,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>41.23655700683594</v>
+        <v>41.23656463623047</v>
       </c>
       <c r="C199" t="n">
         <v>52.43000030517578</v>
@@ -5738,7 +5738,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>40.03472900390625</v>
+        <v>40.03472137451172</v>
       </c>
       <c r="C200" t="n">
         <v>50.5099983215332</v>
@@ -5767,7 +5767,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>35.84975051879883</v>
+        <v>35.8497428894043</v>
       </c>
       <c r="C201" t="n">
         <v>45.22999954223633</v>
@@ -5796,7 +5796,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>34.68460464477539</v>
+        <v>34.68461608886719</v>
       </c>
       <c r="C202" t="n">
         <v>43.7599983215332</v>
@@ -5825,7 +5825,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>36.89599609375</v>
+        <v>36.89599227905273</v>
       </c>
       <c r="C203" t="n">
         <v>46.54999923706055</v>
@@ -5854,7 +5854,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>40.07407379150391</v>
+        <v>40.07408142089844</v>
       </c>
       <c r="C204" t="n">
         <v>50.13000106811523</v>
@@ -5912,7 +5912,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>35.62572860717773</v>
+        <v>35.625732421875</v>
       </c>
       <c r="C206" t="n">
         <v>44.15999984741211</v>
@@ -5970,7 +5970,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>32.91508102416992</v>
+        <v>32.91508483886719</v>
       </c>
       <c r="C208" t="n">
         <v>40.79999923706055</v>
@@ -5999,7 +5999,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>31.37420082092285</v>
+        <v>31.37420463562012</v>
       </c>
       <c r="C209" t="n">
         <v>38.88999938964844</v>
@@ -6028,7 +6028,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>31.00423240661621</v>
+        <v>31.00423431396484</v>
       </c>
       <c r="C210" t="n">
         <v>38.02000045776367</v>
@@ -6086,7 +6086,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>29.73352813720703</v>
+        <v>29.73353385925293</v>
       </c>
       <c r="C212" t="n">
         <v>36.06000137329102</v>
@@ -6115,7 +6115,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>29.17282867431641</v>
+        <v>29.17282485961914</v>
       </c>
       <c r="C213" t="n">
         <v>35.38000106811523</v>
@@ -6202,7 +6202,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>25.46298980712891</v>
+        <v>25.46298789978027</v>
       </c>
       <c r="C216" t="n">
         <v>30.46999931335449</v>
@@ -6260,7 +6260,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>22.97060012817383</v>
+        <v>22.9705982208252</v>
       </c>
       <c r="C218" t="n">
         <v>27.07999992370605</v>
@@ -6289,7 +6289,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>22.52950859069824</v>
+        <v>22.52950668334961</v>
       </c>
       <c r="C219" t="n">
         <v>26.55999946594238</v>
@@ -6318,7 +6318,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>23.5389232635498</v>
+        <v>23.53892517089844</v>
       </c>
       <c r="C220" t="n">
         <v>27.75</v>
@@ -6347,7 +6347,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>21.73215293884277</v>
+        <v>21.73215675354004</v>
       </c>
       <c r="C221" t="n">
         <v>25.6200008392334</v>
@@ -6430,7 +6430,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>26.66733741760254</v>
+        <v>26.66733932495117</v>
       </c>
       <c r="C224" t="n">
         <v>30.54000091552734</v>
@@ -6457,7 +6457,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>25.33134841918945</v>
+        <v>25.33135032653809</v>
       </c>
       <c r="C225" t="n">
         <v>29.01000022888184</v>
@@ -6484,7 +6484,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>25.27022361755371</v>
+        <v>25.27022552490234</v>
       </c>
       <c r="C226" t="n">
         <v>28.94000053405762</v>
@@ -6511,7 +6511,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>24.71138000488281</v>
+        <v>24.71138191223145</v>
       </c>
       <c r="C227" t="n">
         <v>28.29999923706055</v>
@@ -6538,7 +6538,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>23.24188804626465</v>
+        <v>23.24188995361328</v>
       </c>
       <c r="C228" t="n">
         <v>26.20999908447266</v>
@@ -6567,7 +6567,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>23.52565383911133</v>
+        <v>23.52565574645996</v>
       </c>
       <c r="C229" t="n">
         <v>26.53000068664551</v>
@@ -6683,7 +6683,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>22.00357627868652</v>
+        <v>22.00357818603516</v>
       </c>
       <c r="C233" t="n">
         <v>24.40999984741211</v>
@@ -6712,7 +6712,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>21.57822036743164</v>
+        <v>21.57821846008301</v>
       </c>
       <c r="C234" t="n">
         <v>23.48999977111816</v>
@@ -6741,7 +6741,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>22.26718139648438</v>
+        <v>22.26717948913574</v>
       </c>
       <c r="C235" t="n">
         <v>24.23999977111816</v>
@@ -6828,7 +6828,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>23.81014060974121</v>
+        <v>23.81013870239258</v>
       </c>
       <c r="C238" t="n">
         <v>25.47999954223633</v>
@@ -6857,7 +6857,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>23.03453636169434</v>
+        <v>23.0345344543457</v>
       </c>
       <c r="C239" t="n">
         <v>24.64999961853027</v>
